--- a/OUT_EXCEL/out_8.xlsx
+++ b/OUT_EXCEL/out_8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,9 +450,6 @@
       <c r="H1" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -465,33 +462,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ma SV</t>
+          <t>Mã SV</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ho va</t>
+          <t>Họrà</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ten</t>
+          <t>[Têm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lop</t>
+          <t>LớP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Diem R1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Xep loai</t>
+          <t>[Điẻm Rl</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Xếp loai</t>
         </is>
       </c>
     </row>
@@ -506,22 +502,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B20DCKT001</t>
+          <t>BZODCKTOOI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DO Thu</t>
+          <t>|Đỗ Thu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>An</t>
+          <t>@</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -529,10 +525,9 @@
           <t>77</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Khả</t>
         </is>
       </c>
     </row>
@@ -542,36 +537,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B20DCKT004</t>
+          <t>BO5TKIOG7</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dang Thi Kim</t>
+          <t>1z2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Kem</t>
         </is>
@@ -583,38 +577,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B20DCKT006</t>
+          <t>B2O5CKIOD6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ha Thi Mai</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>220</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>75 ......</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RhZ</t>
         </is>
       </c>
     </row>
@@ -624,36 +617,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B20DCKT011</t>
+          <t>B2ODCKTOTI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pham Tuan</t>
+          <t>@Ph?Tz</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Kem</t>
         </is>
@@ -665,36 +657,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B20DCKT016</t>
+          <t>B2ODCKTO16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vu Minh</t>
+          <t>MMi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anh</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Kem</t>
         </is>
@@ -711,22 +702,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B20DCKT029</t>
+          <t>B2ODCKTO29</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bui Quynh</t>
+          <t>17221</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chi</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207277</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -734,10 +725,9 @@
           <t>78</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RhZ</t>
         </is>
       </c>
     </row>
@@ -752,33 +742,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B20DCKT058</t>
+          <t>B2O5CKTO5S</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dang Thi</t>
+          <t>E22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hien</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Tot</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -788,38 +777,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B20DCKT061</t>
+          <t>B2ODCKTO6T</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nguyen Phuc Thu</t>
+          <t>1guynPhicI2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hien</t>
+          <t>1E2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Xuat sac</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Xuts</t>
         </is>
       </c>
     </row>
@@ -829,38 +817,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B20DCKT073</t>
+          <t>BO5CKIO73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dang Khanh</t>
+          <t>ĐặngKhZh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Huyen</t>
+          <t>1E2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7hZ</t>
         </is>
       </c>
     </row>
@@ -870,38 +857,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>70</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B20DCKT080</t>
+          <t>B2ODCKTO8O</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nguyen Thi Thu</t>
+          <t>Nzzyen ThiThu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Huyen</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Tot</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -911,27 +897,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B20DCKT082</t>
+          <t>B2ODCKTO82</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tran Thi</t>
+          <t>Tiiti</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Huyen</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -939,10 +925,9 @@
           <t>79</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -952,38 +937,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B20DCKT083</t>
+          <t>B2O5CKT83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Trinh Thu</t>
+          <t>Tihih</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Huyen</t>
+          <t>1EE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -993,27 +977,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B20DCKT072</t>
+          <t>B2O5CKIO7Z</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tran Thanh</t>
+          <t>Tiihan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hue</t>
+          <t>[</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1021,10 +1005,9 @@
           <t>77</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7hZ</t>
         </is>
       </c>
     </row>
@@ -1034,27 +1017,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B20DCKT046</t>
+          <t>B2ODCKTO76</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nguyen Thu</t>
+          <t>Iz72</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ha</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1062,10 +1045,9 @@
           <t>76</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1075,27 +1057,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B20DCKT047</t>
+          <t>BZODCKTOZT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pham Minh</t>
+          <t>PhamJih</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ha</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1103,10 +1085,9 @@
           <t>79</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Khỉ</t>
         </is>
       </c>
     </row>
@@ -1116,27 +1097,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B20DCKT050</t>
+          <t>B2ODCKTO50</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Le Thi</t>
+          <t>Ez</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hanh</t>
+          <t>Hạh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1144,10 +1125,9 @@
           <t>76</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>7hZ</t>
         </is>
       </c>
     </row>
@@ -1157,38 +1137,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B20DCKT055</t>
+          <t>B2ODCKTO55</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nguyen Thi Le</t>
+          <t>@EZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hang</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Tot</t>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1198,38 +1177,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B20DCKT094</t>
+          <t>1BZO5TKIO57</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Le Thuy</t>
+          <t>EZ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Linh</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Xuat sac</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Xus</t>
         </is>
       </c>
     </row>
@@ -1239,38 +1217,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B20DCKT091</t>
+          <t>1B25CKTO9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vu Thi</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>RhZ</t>
         </is>
       </c>
     </row>
@@ -1285,33 +1262,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B20DCKT120</t>
+          <t>B2O5CKT12</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tran Quang</t>
+          <t>1222222</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Minh</t>
+          <t>TIh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Kem</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Rzm</t>
         </is>
       </c>
     </row>
@@ -1321,38 +1297,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B20DCKT125</t>
+          <t>B2ODCKTI25</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Trinh Thi</t>
+          <t>Trithi</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nga</t>
+          <t>[</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Khỉ</t>
         </is>
       </c>
     </row>
@@ -1367,29 +1342,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B20DCKT128</t>
+          <t>BZODCKTI28</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nguyen Hong</t>
+          <t>[2Eie</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ngan</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>[Ngân</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DZOACCA</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Yeu</t>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Z</t>
         </is>
       </c>
     </row>
@@ -1399,27 +1377,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B20DCKT132</t>
+          <t>B2ODCKTI32</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nguyen Minh</t>
+          <t>TZZh</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ngoc</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1427,10 +1405,9 @@
           <t>76</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>7hZ</t>
         </is>
       </c>
     </row>
@@ -1440,38 +1417,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B20DCKT148</t>
+          <t>B2O5CKTT78</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nguyen Vii Quynh</t>
+          <t>Nzuyễn Vũ Quyzh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nhu</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Kem</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kém</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1457,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B20DCKT159</t>
+          <t>BZODCKTI59</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pham Thi Linh</t>
+          <t>Ph?m ThiINh</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Phuong</t>
+          <t>@E2</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1509,10 +1485,9 @@
           <t>82</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Tot</t>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1522,38 +1497,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B20DCKT165</t>
+          <t>B2ODCKTI65</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Nguyen Thi Huong</t>
+          <t>E322</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Quynh</t>
+          <t>1?2</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>7hZ</t>
         </is>
       </c>
     </row>
@@ -1568,33 +1542,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B20DCKT177</t>
+          <t>BZODCKTI7T</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nguyen Thi Thu</t>
+          <t>TZZIII</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thanh</t>
+          <t>[h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCT</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Kha</t>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1609,33 +1582,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B20DCKT197</t>
+          <t>BZODCKTI97</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dong Thi Le</t>
+          <t>|622</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>...... 36</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Yeu.</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1645,36 +1617,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>729</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B20DCKT210</t>
+          <t>BZODCKT2IO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ngo Thi Hoai</t>
+          <t>[7zõ Th7Hoz</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thuong</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+          <t>729</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Kem</t>
         </is>
@@ -1691,33 +1662,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B20DCKT212</t>
+          <t>B2O5CKIZI2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DO Thi Thu</t>
+          <t>1TIhiIhu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trang</t>
+          <t>Ezi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACTF</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Kem</t>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>K22</t>
         </is>
       </c>
     </row>
@@ -1727,27 +1697,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B20DCKT213</t>
+          <t>BZODCKT2I3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hoang Thu</t>
+          <t>Hoang ThG</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trang</t>
+          <t>Iz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1755,10 +1725,9 @@
           <t>74</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Khả</t>
         </is>
       </c>
     </row>
@@ -1768,38 +1737,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B20DCKT214</t>
+          <t>BZODTRIZI7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Nguyen Quynh</t>
+          <t>TzzyễnQz2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trang</t>
+          <t>Irng</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>5207227</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Tot</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1809,27 +1777,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B20DCKT222</t>
+          <t>B2ODCKIZ2Z</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tran Phuong</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Trinh</t>
+          <t>[iinh</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>I2O72&lt;7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1837,10 +1805,9 @@
           <t>76</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Kha</t>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>7hZ</t>
         </is>
       </c>
     </row>
@@ -1855,22 +1822,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B20DCKT211</t>
+          <t>BZODCKT2II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kieu Thu</t>
+          <t>K Thu</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tra</t>
+          <t>Trà</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>D20ACCA</t>
+          <t>DZOACCA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1878,10 +1845,9 @@
           <t>85</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Tot</t>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>7ẫt</t>
         </is>
       </c>
     </row>
